--- a/Готовый_список_товаров.xlsx
+++ b/Готовый_список_товаров.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T87"/>
+  <dimension ref="A1:T116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,17 +529,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Оптовая продажа: бытовой электронный прибор для ухода за кожей, аппарат для красоты лица и губ, массажер для глаз, вибрационный прибор для лица.</t>
+          <t>Крем для рук Runpei Roopy с натуральным ароматом, вязкостью и нежирностью, портативная упаковка круглый год.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01IeISKp1Qaq29opxHd_!!2209856751993-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01cSWguF1I8QxpMEYdH_!!2215324090848-0-cib.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F643248323511.html&amp;q=1&amp;t=1773241535738&amp;tep=FKFXRMKNN1617229&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F990682256636.html&amp;q=1&amp;t=1773831956767&amp;tep=PFWXKQKNN2225620&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -548,28 +548,28 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: Калифорнийское солнце, таблетка 2 г</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>043</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>2150.00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>2150.00</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Корейский антиоксидантный крем для лица Dr. Althea 345, реализуемый через границу: увлажняющий, питательный, восстанавливающий кожный барьер, успокаивающий, подходит для</t>
+          <t>YIMIAOSI 30г 10 Вкус Увлажняющий Увлажняющий Оптовая продажа</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01cG7kuz2BOjxG9oG6w_!!2220867888329-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01M2IkZt2B2kpYKok83_!!2874618281-0-cib.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F986745758911.html&amp;q=1&amp;t=1773241535739&amp;tep=FKFXRMKNN392324&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F854336156155.html&amp;q=1&amp;t=1773831956769&amp;tep=PFWXKQKNN952526&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -606,7 +606,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: №0905-Отбеливающий крем для рук [Жасмин]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -616,18 +616,18 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>039</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -645,17 +645,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Летние ультратонкие воздухопроницаемые вязаные наколенники для мужчин и женщин</t>
+          <t>YIMIAOSI 30г 10 Вкус Увлажняющий Увлажняющий Оптовая продажа</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01lkN51p1fIGVzzHsxS_!!2218423473983-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01Y2egG22B2kpbusZMV_!!2874618281-0-cib.jpg</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F828163742889.html&amp;q=1&amp;t=1773241535740&amp;tep=FKFXRMKNN23161611&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F854336156155.html&amp;q=1&amp;t=1773831956770&amp;tep=PFWXKQKNN725213&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -664,7 +664,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Характеристики: Полый цвет кожи</t>
+          <t>Характеристики: №0868-Отбеливающий крем для рук [Хими дыня]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -674,18 +674,18 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>039</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -703,17 +703,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+          <t>YIMIAOSI 30г 10 Вкус Увлажняющий Увлажняющий Оптовая продажа</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01fHvIED1DS3ppejORl_!!2218586030214-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN017baQyN2B2kpbCvyoK_!!2874618281-0-cib.jpg</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773241535741&amp;tep=FKFXRMKNN414514&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F854336156155.html&amp;q=1&amp;t=1773831956772&amp;tep=PFWXKQKNN138517&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -722,28 +722,28 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Характеристики: цветная коробка</t>
+          <t>Характеристики: №0899 - Отбеливающий крем для рук [Персик]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>039</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -761,17 +761,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+          <t>YIMIAOSI 30г 10 Вкус Увлажняющий Увлажняющий Оптовая продажа</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01L32e8e1DS3kQm564i_!!2218586030214-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01zZz0CD2B2kpZgnV4P_!!2874618281-0-cib.jpg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773241535743&amp;tep=FKFXRMKNN3262421&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F854336156155.html&amp;q=1&amp;t=1773831956774&amp;tep=PFWXKQKNN1820115&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -780,28 +780,28 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Характеристики: полуденный фиолетовый</t>
+          <t>Характеристики: №0851 - Отбеливающий крем для рук [Клубника]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>039</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -819,17 +819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+          <t>YIMIAOSI 30г 10 Вкус Увлажняющий Увлажняющий Оптовая продажа</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01BXfNfE1DS3kQm7Rfz_!!2218586030214-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01AymhKL2B2kpcXeFuv_!!2874618281-0-cib.jpg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773241535745&amp;tep=FKFXRMKNN642413&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F854336156155.html&amp;q=1&amp;t=1773831956774&amp;tep=PFWXKQKNN1821215&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -838,28 +838,28 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Характеристики: Матча зеленый</t>
+          <t>Характеристики: №0769-Отбеливающий крем для рук [Лимон]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>039</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>390.00</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -877,17 +877,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+          <t>MINSHZEE Mingxizhi Повседневная, защищенная от пота для новичков, коричнево-белая, угловая</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01UstgiQ1DS3kQm4tcw_!!2218586030214-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01rzWAv81ycOZNMAppK_!!2217545266599-0-cib.jpg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773241535746&amp;tep=FKFXRMKNN268516&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F772455779496.html&amp;q=1&amp;t=1773831956775&amp;tep=PFWXKQKNN20222612&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -896,28 +896,28 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Характеристики: Монетный порошок</t>
+          <t>Характеристики: 03 #серо-коричневый_</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -935,17 +935,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Красочные массажные подушечки для ног EMS, красивые ноги, подушечки для массажа ступни и ног, вибрационные импульсные массажные подушечки для расслабления ног</t>
+          <t>MINSHZEE Mingxizhi Повседневная, защищенная от пота для новичков, коричнево-белая, угловая</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN0121CDTz1srcBgihRPh_!!2208534405820-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01P2owRA1ycOZPgdAlb_!!2217545266599-0-cib.jpg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F915276878789.html&amp;q=1&amp;t=1773241535747&amp;tep=FKFXRMKNN7151614&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F772455779496.html&amp;q=1&amp;t=1773831956776&amp;tep=PFWXKQKNN12099&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -954,28 +954,28 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Характеристики: Красочная массажная подушечка для ног [перезаряжается с помощью пульта дистанционного управления]</t>
+          <t>Характеристики: 01 # Черный</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>50.90</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>101.80</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>101.80</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -993,17 +993,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Массажер для ног, массажер для икроножных мышц, устройство для прочистки меридианов, массажер для варикозного расширения вен, полностью автоматический электрический массажер для ног,</t>
+          <t>MINSHZEE Mingxizhi Повседневная, защищенная от пота для новичков, коричнево-белая, угловая</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01BEPsqX21353ZlV9xr_!!2200736906928-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01P2owRA1ycOZPgdAlb_!!2217545266599-0-cib.jpg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1004363871327.html&amp;q=1&amp;t=1773241535747&amp;tep=FKFXRMKNN1620168&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F772455779496.html&amp;q=1&amp;t=1773831956776&amp;tep=PFWXKQKNN1921120&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1012,28 +1012,28 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Характеристики: Темно-серый + 1 шт.; английская упаковка.</t>
+          <t>Характеристики: 02 # натуральный коричневый</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>65.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>325.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>325.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1051,17 +1051,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Водонепроницаемые бандажи для ног, защита послеоперационных ран, гипсовые повязки, средства от травм рук и ног, принадлежности для купания голеностопных суставов и ног,</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01XjKQ542BvG24IbdDJ_!!2219496988400-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>PEACH JO+ Эссенция для губ с ромашкой и медом, увлажняющее и питательное масло для губ для женщин, подарок на День святого Валентина</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773241535748&amp;tep=FKFXRMKNN42073&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F890276737232.html&amp;q=1&amp;t=1773831956777&amp;tep=PFWXKQKNN10141516&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1070,28 +1066,28 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Характеристики: Взрослые короткие леггинсы с усиленной резинкой для предотвращения скольжения; универсальный размер.</t>
+          <t>Характеристики: [PEACH JO+Успокаивающее масло для губ из немецких ромашек] 4 мл</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>56.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>284.00</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>284.00</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1109,17 +1105,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Водонепроницаемые бандажи для ног, защита послеоперационных ран, гипсовые повязки, средства от травм рук и ног, принадлежности для купания голеностопных суставов и ног,</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01Bz0ijR2BvG23inPuj_!!2219496988400-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>PEACH JO+ Эссенция для губ с ромашкой и медом, увлажняющее и питательное масло для губ для женщин, подарок на День святого Валентина</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773241535749&amp;tep=FKFXRMKNN619257&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F890276737232.html&amp;q=1&amp;t=1773831956778&amp;tep=PFWXKQKNN22211&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1128,28 +1120,28 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Характеристики: /Регулируемая по высоте высота ножек для взрослых (подходит для икр и ниже)/; /Универсальный размер/</t>
+          <t>Характеристики: Многоцелевое эфирное масло папайи 4мл.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>38.60</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>193.00</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>193.00</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1167,17 +1159,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Водонепроницаемые бандажи для ног, защита послеоперационных ран, гипсовые повязки, средства от травм рук и ног, принадлежности для купания голеностопных суставов и ног,</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01rwwHTO2BvG24m7LlQ_!!2219496988400-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>PEACH JO+ Эссенция для губ с ромашкой и медом, увлажняющее и питательное масло для губ для женщин, подарок на День святого Валентина</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773241535750&amp;tep=FKFXRMKNN1313173&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F890276737232.html&amp;q=1&amp;t=1773831956778&amp;tep=PFWXKQKNN418256&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1186,28 +1174,28 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Характеристики: Взрослые короткие леггинсы; Универсальный размер</t>
+          <t>Характеристики: [PEACH JO+ Американское успокаивающее масло для губ маленькой девочки с синей трубкой] 4 мл</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>46.40</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>232.00</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>232.00</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1225,17 +1213,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Водонепроницаемые бандажи для ног, защита послеоперационных ран, гипсовые повязки, средства от травм рук и ног, принадлежности для купания голеностопных суставов и ног,</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01ngMSXF2BvG241xgTJ_!!2219496988400-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Электропилка для ног, шлифовальная машинка для ног, триммер для ног, удаляет омертвевшую кожу и мозоли, инструмент для полировки ног, аксессуары.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773241535752&amp;tep=FKFXRMKNN1211722&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1011781834825.html&amp;q=1&amp;t=1773831956779&amp;tep=PFWXKQKNN11242415&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1244,28 +1228,28 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Характеристики: /Взрослая футболка с коротким рукавом/; /Универсальный размер/</t>
+          <t>Характеристики: 60 штук в коробке; шлифовальные подушки</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>206.00</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>206.00</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1283,17 +1267,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Гипсовые туфли для поврежденных ног, обувь послеоперационная при вальгусной деформации, опухших ног, высоких ног, деформированных ног, защитная обувь при переломе подошвы.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN0107NxKJ1p57PVpfMKa_!!2220705835308-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Инструмент для шлифовки ногтей Электрический инструмент для снятия ногтей</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F980434630582.html&amp;q=1&amp;t=1773241535753&amp;tep=FKFXRMKNN1321920&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F886172033289.html&amp;q=1&amp;t=1773831956779&amp;tep=PFWXKQKNN2221717&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1302,7 +1282,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Характеристики: М.; Все включено послеоперационная обувь [одиночная]</t>
+          <t>Характеристики: Выбран индивидуальный сервис</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1341,17 +1321,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Гипсовые туфли для поврежденных ног, обувь послеоперационная при вальгусной деформации, опухших ног, высоких ног, деформированных ног, защитная обувь при переломе подошвы.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN0107NxKJ1p57PVpfMKa_!!2220705835308-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Инструмент для шлифовки ногтей Электрический инструмент для снятия ногтей</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F980434630582.html&amp;q=1&amp;t=1773241535754&amp;tep=FKFXRMKNN13141112&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F886172033289.html&amp;q=1&amp;t=1773831956780&amp;tep=PFWXKQKNN10134&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1360,7 +1336,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Характеристики: XL;</t>
+          <t>Характеристики: Выбран индивидуальный сервис</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1370,18 +1346,18 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>49.00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>98.00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>98.00</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1399,17 +1375,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Гипсовые туфли для поврежденных ног, обувь послеоперационная при вальгусной деформации, опухших ног, высоких ног, деформированных ног, защитная обувь при переломе подошвы.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN0107NxKJ1p57PVpfMKa_!!2220705835308-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Инструмент для шлифовки ногтей Электрический инструмент для снятия ногтей</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F980434630582.html&amp;q=1&amp;t=1773241535754&amp;tep=FKFXRMKNN1122423&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F886172033289.html&amp;q=1&amp;t=1773831956781&amp;tep=PFWXKQKNN10101914&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1418,7 +1390,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Характеристики: Л; Все включено послеоперационная обувь [одиночная]</t>
+          <t>Характеристики: Выбран индивидуальный сервис</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1457,17 +1429,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Обувь для ходьбы Hong Sheng, регулируемые ортопедические ботинки с воздушной подушкой для ахиллова сухожилия, бандажи для фиксации голеностопного сустава и стопы</t>
+          <t>Инструмент для шлифовки ногтей Электрический инструмент для снятия ногтей</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN012SZzK42A3q5QXIIyY_!!3446678148-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01LRHi7J1Sf5ICwZ8YE_!!3343492273-0-cib.jpg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F778091504347.html&amp;q=1&amp;t=1773241535755&amp;tep=FKFXRMKNN721124&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F886172033289.html&amp;q=1&amp;t=1773831956782&amp;tep=PFWXKQKNN8722&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1476,7 +1448,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Характеристики: Черный; XL</t>
+          <t>Характеристики: Выбран индивидуальный сервис</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1486,18 +1458,18 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -1515,17 +1487,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Обувь для ходьбы Hong Sheng, регулируемые ортопедические ботинки с воздушной подушкой для ахиллова сухожилия, бандажи для фиксации голеностопного сустава и стопы</t>
+          <t>Прямые продажи с фабрики, перезаряжаемый массажер для глаз, умное устройство для защиты</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN012SZzK42A3q5QXIIyY_!!3446678148-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/3197523840_1460157355.jpg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F778091504347.html&amp;q=1&amp;t=1773241535756&amp;tep=FKFXRMKNN822219&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F545416647440.html&amp;q=1&amp;t=1773831956782&amp;tep=PFWXKQKNN28612&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1534,28 +1506,28 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Характеристики: Черный; Л</t>
+          <t>Характеристики: +USB-кабель + руководство на английском языке; Черный</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -1573,17 +1545,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Обувь для ходьбы Hong Sheng, регулируемые ортопедические ботинки с воздушной подушкой для ахиллова сухожилия, бандажи для фиксации голеностопного сустава и стопы</t>
+          <t>Воздушная подушка Дноглубокие щетки для всего тела Универсальный соскоб массажный инструмент для живота мягкие щетки для ног Домашний массажер</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN012SZzK42A3q5QXIIyY_!!3446678148-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN015BBrc21SbsYSSVF9P_!!2214161252266-0-cib.jpg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F778091504347.html&amp;q=1&amp;t=1773241535757&amp;tep=FKFXRMKNN211917&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F785513320546.html&amp;q=1&amp;t=1773831956783&amp;tep=PFWXKQKNN5171613&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1592,28 +1564,28 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Характеристики: Черный; М</t>
+          <t>Характеристики: Массажная щетка из бука без гвоздей + эфирное масло</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -1631,17 +1603,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Регулируемый фиксатор плечевого и локтевого суставов при переломах лучевой и локтевой костей, поддержка плечевой кости, шина для руки и верхней конечности, ортез при вывихе плеча.</t>
+          <t>Интеллектуальный импульсный массажер для ног с имитацией человеческого разминания, индивидуальное OEM-производство.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01V5EAJE1XKXNtBT7yR_!!2919502905-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yvOXmf1H2eL7LdViS_!!2220412450700-0-cib.jpg</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F704269019742.html&amp;q=1&amp;t=1773241535758&amp;tep=FKFXRMKNN2617215&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F980978658187.html&amp;q=1&amp;t=1773831956784&amp;tep=PFWXKQKNN236817&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1650,7 +1622,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Характеристики: Фиксирующий бандаж для плечевого и локтевого суставов; универсальный размер.</t>
+          <t>Характеристики: Черный 32-х уровневый микроток для разминания</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1660,18 +1632,18 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>225.00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>225.00</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -1689,17 +1661,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+          <t>Новая колонка для сна, устанавливаемая на подушку, отличный инструмент для прослушивания музыки, мини-колонка Bluetooth, которая поможет вам спать под подушкой ( оптовая продажа,</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01nokGCf1XKXWaBwBS7_!!2919502905-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01l4BNPL1H2eMpR7Zg4_!!2220412450700-0-cib.jpg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773241535760&amp;tep=FKFXRMKNN101229&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1019929524551.html&amp;q=1&amp;t=1773831956785&amp;tep=PFWXKQKNN1142211&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1708,28 +1680,28 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Характеристики: Слинг для взрослых; Справа.</t>
+          <t>Характеристики: Оранжевый; английский</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -1747,17 +1719,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+          <t>Массажер для головы Octopus, машинный вибрационный массажер для разблокировки и расслабления меридианов, массаж головы восемью щупальцами.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01nokGCf1XKXWaBwBS7_!!2919502905-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01i6tyMA21hqF9FMetn_!!2208977077017-0-cib.jpg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773241535760&amp;tep=FKFXRMKNN71077&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F913700383616.html&amp;q=1&amp;t=1773831956785&amp;tep=PFWXKQKNN1791322&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1766,7 +1738,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Характеристики: Слинг для взрослых; Слева</t>
+          <t>Характеристики: Модель 810-Bluetooth; черный</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1776,18 +1748,18 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>375.00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>375.00</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
@@ -1805,17 +1777,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+          <t>Умный тренажер для прыжков со скакалкой с Bluetooth для взрослых и детей, увлекательная тренировка, автоматический электронный подсчет, электрический тренажер для фитнеса и похудения, возможность использования</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01nokGCf1XKXWaBwBS7_!!2919502905-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN014Zl8c621hqJsGwna4_!!2208977077017-0-cib.jpg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773241535761&amp;tep=FKFXRMKNN1131523&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1028508757393.html&amp;q=1&amp;t=1773831956786&amp;tep=PFWXKQKNN16161216&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1824,7 +1796,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Характеристики: Взрослые; Справа.</t>
+          <t>Характеристики: [Лимоново-желтый] 10-скоростной режим работы/Пульт дистанционного управления/Bluetooth/USB-зарядка</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1834,18 +1806,18 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>45.60</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
@@ -1863,17 +1835,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+          <t>Умный тренажер для прыжков со скакалкой с Bluetooth для взрослых и детей, увлекательная тренировка, автоматический электронный подсчет, электрический тренажер для фитнеса и похудения, возможность использования</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01nokGCf1XKXWaBwBS7_!!2919502905-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN014Zl8c621hqJsGwna4_!!2208977077017-0-cib.jpg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773241535762&amp;tep=FKFXRMKNN12191520&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1028508757393.html&amp;q=1&amp;t=1773831956787&amp;tep=PFWXKQKNN522221&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1882,7 +1854,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Характеристики: Взрослые; Слева</t>
+          <t>Характеристики: [Мятно-зеленый] 10-скоростная регулировка / Пульт дистанционного управления / Bluetooth/USB-зарядка</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1892,18 +1864,18 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>45.60</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
@@ -1921,17 +1893,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Регулируемый бандаж для фиксации локтевого сустава, поддерживающая повязка при переломе руки, противовывиховый бандаж, послеоперационный реабилитационный бандаж.</t>
+          <t>Умный тренажер для прыжков со скакалкой с Bluetooth для взрослых и детей, увлекательная тренировка, автоматический электронный подсчет, электрический тренажер для фитнеса и похудения, возможность использования</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01S6w4NP1XKXJMCLTHX_!!2919502905-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN014Zl8c621hqJsGwna4_!!2208977077017-0-cib.jpg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F668295944038.html&amp;q=1&amp;t=1773241535763&amp;tep=FKFXRMKNN1317166&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1028508757393.html&amp;q=1&amp;t=1773831956789&amp;tep=PFWXKQKNN5251811&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1940,28 +1912,28 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Характеристики: Модель с подлокотником; правая</t>
+          <t>Характеристики: 【Нежный розовый】10 режимов скорости/Пульт дистанционного управления/Bluetooth/USB-зарядка</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>45.60</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
@@ -1979,17 +1951,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Регулируемый бандаж для фиксации локтевого сустава, поддерживающая повязка при переломе руки, противовывиховый бандаж, послеоперационный реабилитационный бандаж.</t>
+          <t>Умный тренажер для прыжков со скакалкой с Bluetooth для взрослых и детей, увлекательная тренировка, автоматический электронный подсчет, электрический тренажер для фитнеса и похудения, возможность использования</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01S6w4NP1XKXJMCLTHX_!!2919502905-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN014Zl8c621hqJsGwna4_!!2208977077017-0-cib.jpg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F668295944038.html&amp;q=1&amp;t=1773241535764&amp;tep=FKFXRMKNN1521111&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1028508757393.html&amp;q=1&amp;t=1773831956790&amp;tep=PFWXKQKNN181785&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1998,28 +1970,28 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Характеристики: С подлокотником; слева</t>
+          <t>Характеристики: [Небесно-голубой] 10-скоростная регулировка / Пульт дистанционного управления / Bluetooth/USB-зарядка</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>45.60</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>228.00</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
@@ -2037,17 +2009,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Грудопоясничный фиксатор, послеоперационный реабилитационный ортез при компрессионных переломах, поддержка позвоночника, термопластичный поясничный поддерживающий каркас для взрослых.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01UZGT2m1XKXWzvQ9v4_!!2919502905-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Лечен массаж шейного отдела позвоночника</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F801057770124.html&amp;q=1&amp;t=1773241535765&amp;tep=FKFXRMKNN20172212&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F633658361562.html&amp;q=1&amp;t=1773831956791&amp;tep=PFWXKQKNN2141023&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2056,7 +2024,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Характеристики: Дышащая конструкция с двумя подушками безопасности; XL</t>
+          <t>Характеристики: Красный свет нагрев усиленная версия продления фюзеляжа золото</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2066,18 +2034,18 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>146.00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>146.00</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
@@ -2095,17 +2063,13 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Грудопоясничный фиксатор, послеоперационный реабилитационный ортез при компрессионных переломах, поддержка позвоночника, термопластичный поясничный поддерживающий каркас для взрослых.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01UZGT2m1XKXWzvQ9v4_!!2919502905-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Лечен массаж шейного отдела позвоночника</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F801057770124.html&amp;q=1&amp;t=1773241535766&amp;tep=FKFXRMKNN2322522&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F633658361562.html&amp;q=1&amp;t=1773831956792&amp;tep=PFWXKQKNN94817&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2114,7 +2078,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Характеристики: Дышащая конструкция с двумя подушками безопасности; M</t>
+          <t>Характеристики: Красный свет нагрев усиленная версия удлинения фюзеляжа красный</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2124,18 +2088,18 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>146.00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>146.00</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
@@ -2153,17 +2117,13 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Грудопоясничный фиксатор, послеоперационный реабилитационный ортез при компрессионных переломах, поддержка позвоночника, термопластичный поясничный поддерживающий каркас для взрослых.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01UZGT2m1XKXWzvQ9v4_!!2919502905-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Лечен массаж шейного отдела позвоночника</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F801057770124.html&amp;q=1&amp;t=1773241535766&amp;tep=FKFXRMKNN8252416&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F633658361562.html&amp;q=1&amp;t=1773831956792&amp;tep=PFWXKQKNN518231&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2172,7 +2132,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Характеристики: Дышащая конструкция с двумя подушками безопасности; L</t>
+          <t>Характеристики: Усиленная версия (элегантная золотая сетка)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2182,18 +2142,18 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>58.00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>116.00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>116.00</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
@@ -2211,17 +2171,13 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Фиксированный сустав бедра травма коленного сустава предоперационная и послеоперационная фиксированная реабилитация</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/2020/188/163/19807361881_553590667.jpg</t>
-        </is>
-      </c>
+          <t>Автоматический массажер для головы с подушками безопасности для сна, тепловой терапии и расслабления; электрический массажер для домашнего использования, с функцией тепловой терапии.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F625565395164.html&amp;q=1&amp;t=1773241535767&amp;tep=FKFXRMKNN711421&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1009733479351.html&amp;q=1&amp;t=1773831956793&amp;tep=PFWXKQKNN23191122&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -2230,28 +2186,28 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Характеристики: Свободный Размер; Левая и правая регулируемые</t>
+          <t>Характеристики: Версия для тепловой терапии с использованием подушки безопасности (без колпачка)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>158.00</t>
+          <t>86.00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>316.00</t>
+          <t>344.00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>316.00</t>
+          <t>344.00</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
@@ -2269,13 +2225,13 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Смешанная</t>
+          <t>Трансграничный массажер для ног для физиотерапии, многофункциональная машина подогрева запястий и лодыжек, теплый горячий компресс, вибрационный массажер</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F925594684653.html&amp;q=1&amp;t=1773241535768&amp;tep=FKFXRMKNN2492615&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F988211336458.html&amp;q=1&amp;t=1773831956794&amp;tep=PFWXKQKNN22171723&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -2284,28 +2240,28 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Характеристики: английский; AA003 массажная расческа с распылителем (розовая)</t>
+          <t>Характеристики: тье нет</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>38.90</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>194.50</t>
+          <t>240.00</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>194.50</t>
+          <t>240.00</t>
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
@@ -2323,13 +2279,13 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Мазь Bao En Tang Weifuling, аутентичный крем Weifuling, антибактериальная травяная мазь Weifuling для наружного применения против зуда</t>
+          <t>Оптовая продажа: бытовой электронный прибор для ухода за кожей, аппарат для красоты лица и губ, массажер для глаз, вибрационный прибор для лица.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F725110083300.html&amp;q=1&amp;t=1773241535769&amp;tep=FKFXRMKNN2311227&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F643248323511.html&amp;q=1&amp;t=1773831956794&amp;tep=PFWXKQKNN7241411&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -2348,18 +2304,18 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
@@ -2377,17 +2333,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ядовитая кожа Король Антибактериальный крем Банг Бай Занят Яд Кожа Король Мазь Крем для натуральной кожи Натуральные товарысмешанная</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01mvB0pe1Y0DUwz19g3_!!2209994362996-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Корейский антиоксидантный крем 345, Смешанная</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F724775389538.html&amp;q=1&amp;t=1773241535770&amp;tep=FKFXRMKNN1451422&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F986745758911.html&amp;q=1&amp;t=1773831956795&amp;tep=PFWXKQKNN2131714&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -2406,18 +2358,18 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
@@ -2435,17 +2387,13 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Кан Традиционная полость рта Освежение полости рта Смешанная</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01F8x3581Y0Deq1tiDr_!!2209994362996-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Летние ультратонкие воздухопроницаемые вязаные наколенники для мужчин и женщин</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F902962451285.html&amp;q=1&amp;t=1773241535771&amp;tep=FKFXRMKNN4261316&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F828163742889.html&amp;q=1&amp;t=1773831956796&amp;tep=PFWXKQKNN44188&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -2454,7 +2402,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: Полый цвет кожи</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2464,18 +2412,18 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
@@ -2493,17 +2441,13 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Xianzhi Fu Ba Skin Poison Fresh Xianzhi Beijing Kangning Tianzhi Skin Poison Очищающая мазь против анестезиа кожи Крем Другиесмешанная</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01NrwnRM1Y0DirrJFWx_!!2209994362996-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1001577817475.html&amp;q=1&amp;t=1773241535771&amp;tep=FKFXRMKNN1912823&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773831956797&amp;tep=PFWXKQKNN1251026&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2512,28 +2456,28 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: цветная коробка</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
@@ -2551,17 +2495,13 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Royal Grass Zhen Ding B Оральная паста 65 г/тюбик для пародонтального ухода за красными и опухолевыми деснами, зубная паста Канчинин, антибактериальный тип Кан традиционной китайской медицины.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01Q72Z7W1Y0DeoiB3oN_!!2209994362996-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F902965743360.html&amp;q=1&amp;t=1773241535772&amp;tep=FKFXRMKNN21276&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773831956797&amp;tep=PFWXKQKNN13121112&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2570,28 +2510,28 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: полуденный фиолетовый</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>29.80</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>29.80</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -2609,17 +2549,13 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Крем Shulijia Anti-Drug Cream, травяная мазь Jiangxi Honghai Herbal Ointment, мазь для наружного применения, доступна в больших количествах для оптовых</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01eOpV341Vv3gj6Nd3o_!!2210100902714-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F725115135011.html&amp;q=1&amp;t=1773241535773&amp;tep=FKFXRMKNN12121417&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773831956798&amp;tep=PFWXKQKNN1824179&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2628,28 +2564,28 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: Матча зеленый</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>17.20</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>17.20</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
@@ -2665,15 +2601,15 @@
           <t>+380936174140</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01sJL2y31Y0DiUXzBZP_!!2209994362996-0-cib.jpg</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ролик для йоги, подошвенной фасции, мышц ног, релаксации, фитнеса, арки стопы, массажа</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F993297925846.html&amp;q=1&amp;t=1773241535774&amp;tep=FKFXRMKNN2211819&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F834107964423.html&amp;q=1&amp;t=1773831956799&amp;tep=PFWXKQKNN1314239&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2682,28 +2618,28 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: Монетный порошок</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="R39" t="inlineStr"/>
@@ -2719,15 +2655,15 @@
           <t>+380936174140</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01978lT81Vv3gh9hd3P_!!2210100902714-0-cib.jpg</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Красочные массажные подушечки для ног EMS, красивые ноги, подушечки для массажа подошв и ног, вибрационные импульсные массажные подушечки для расслабления ног</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F724930778595.html&amp;q=1&amp;t=1773241535775&amp;tep=FKFXRMKNN214255&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F915276878789.html&amp;q=1&amp;t=1773831956799&amp;tep=PFWXKQKNN8212019&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2736,28 +2672,28 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: Красочная массажная подушечка для ног [перезаряжаемая с помощью пульта дистанционного управления]</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>50.90</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>101.80</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>101.80</t>
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
@@ -2775,17 +2711,13 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Крем Bangbai Mangbaodu Baowang Baodu Baowang Крем для кожи Травяной наружный крем против акустики и</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01733rcd1Vv3rZcaqLC_!!2210100902714-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>腿部按摩器小腿肌肉神仪经络疏通静脉曲张电动全自动揉捏足疗机器</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F651595883228.html&amp;q=1&amp;t=1773241535776&amp;tep=FKFXRMKNN22131721&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1004363871327.html&amp;q=1&amp;t=1773831956800&amp;tep=PFWXKQKNN74254&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2794,28 +2726,28 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: 深灰色+1只装; 英文包装</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>65.00</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>43.60</t>
+          <t>325.00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>43.60</t>
+          <t>325.00</t>
         </is>
       </c>
       <c r="R41" t="inlineStr"/>
@@ -2833,17 +2765,13 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Мяо Цзя Ланчжун</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01orVHmf1Vv3vlvyGgb_!!2210100902714-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>骨洗澡防水套脚术后伤口保护套打石膏手脚受伤脚踝腿部洗澡神器</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F645399027304.html&amp;q=1&amp;t=1773241535778&amp;tep=FKFXRMKNN31614&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773831956800&amp;tep=PFWXKQKNN2112192&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2852,28 +2780,28 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: /成人短款腿部【橡胶加强防滑】/; /均码/</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>56.80</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>21.80</t>
+          <t>284.00</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>21.80</t>
+          <t>284.00</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -2891,13 +2819,13 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Травяной крем Ice Wave Silkworm для детской кожи, противозудная мазь Ice Silkworm для наружного применения</t>
+          <t>骨洗澡防水套脚术后伤口保护套打石膏手脚受伤脚踝腿部洗澡神器</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F642315882168.html&amp;q=1&amp;t=1773241535778&amp;tep=FKFXRMKNN1351114&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773831956801&amp;tep=PFWXKQKNN1511510&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -2906,28 +2834,28 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: /成人加高足部（适合小腿及以下使用）/; /均码/</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>38.60</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>193.00</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>193.00</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
@@ -2945,13 +2873,13 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Зарубежный крем Чичеллы Миллион, внешний крем для кожи, внешний крем для кожи Чичеллы Миллион, крем против полиэтилена, цельныйсмешанная</t>
+          <t>骨洗澡防水套脚术后伤口保护套打石膏手脚受伤脚踝腿部洗澡神器</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F659242299733.html&amp;q=1&amp;t=1773241535779&amp;tep=FKFXRMKNN16276&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773831956801&amp;tep=PFWXKQKNN25182125&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2960,28 +2888,28 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Характеристики: Нет технических характеристик</t>
+          <t>Характеристики: /成人短款腿部/; /均码/</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>46.40</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>232.00</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>232.00</t>
         </is>
       </c>
       <c r="R44" t="inlineStr"/>
@@ -2999,13 +2927,13 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Наколенники из чистого хлопка с экстрактом полыни, унисекс, теплые, бесшовные, тонкие, защита коленных суставов, согревающие наколенники для тех, у кого мерзнут ноги.</t>
+          <t>骨洗澡防水套脚术后伤口保护套打石膏手脚受伤脚踝腿部洗澡神器</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F731863776117.html&amp;q=1&amp;t=1773241535780&amp;tep=FKFXRMKNN17242118&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F956174884313.html&amp;q=1&amp;t=1773831956802&amp;tep=PFWXKQKNN12261026&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3014,7 +2942,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Характеристики: Серый + Серый [комплект из 2 пар]; Один размер [80-150 фунтов]</t>
+          <t>Характеристики: /成人短款手臂/; /均码/</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3024,18 +2952,18 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>206.00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>206.00</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
@@ -3053,13 +2981,13 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Наколенники из чистого хлопка с экстрактом полыни, унисекс, теплые, бесшовные, тонкие, защита коленных суставов, согревающие наколенники для тех, у кого мерзнут ноги.</t>
+          <t>Гипсовые туфли для поврежденных ног, обувь послеоперационная при вальгусной деформации, опухших ногах, широких ногах, деформированных ногах, защитная обувь при переломе подошвы.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F731863776117.html&amp;q=1&amp;t=1773241535781&amp;tep=FKFXRMKNN1312158&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F980434630582.html&amp;q=1&amp;t=1773831956802&amp;tep=PFWXKQKNN111772&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3068,28 +2996,28 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Характеристики: Цвет кожи + цвет кожи [2 пары]; Универсальный размер [80-150 фунтов]</t>
+          <t>Характеристики: М.; Все включено послеоперационная обувь [одиночная]</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="R46" t="inlineStr"/>
@@ -3107,13 +3035,13 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Наколенник на шнуровке с подогревом полыни старые холодные ноги теплый ФИЗИОТЕРАПЕВТИЧЕСКИЙ спортивный чехол для давления на ноги Спортивный нескользящий наколенник для мужчин и женщин</t>
+          <t>Гипсовые туфли для поврежденных ног, обувь послеоперационная при вальгусной деформации, опухших ногах, широких ногах, деформированных ногах, защитная обувь при переломе подошвы.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F684403797511.html&amp;q=1&amp;t=1773241535782&amp;tep=FKFXRMKNN422426&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F980434630582.html&amp;q=1&amp;t=1773831956803&amp;tep=PFWXKQKNN2515191&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3122,28 +3050,28 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Характеристики: Размер М (40-60 кг);</t>
+          <t>Характеристики: XL; Все включено послеоперационная обувь [одиночная]</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>32.50</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>32.50</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -3161,13 +3089,13 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Массажер для талии с подушками, подтягивающий и растягивающий, с вибрационной поддержкой поясницы, вибрацией для спины, для домашнего использования, с горячим компрессом, импульсный массажер для поясничного отдела, смешанная</t>
+          <t>Гипсовые туфли для поврежденных ног, обувь послеоперационная при вальгусной деформации, опухших ногах, широких ногах, деформированных ногах, защитная обувь при переломе подошвы.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F921340341364.html&amp;q=1&amp;t=1773241535782&amp;tep=FKFXRMKNN1521144&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F980434630582.html&amp;q=1&amp;t=1773831956804&amp;tep=PFWXKQKNN102188&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3176,7 +3104,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Характеристики: Зеленый - массаж верхней части талии + горячий компресс с красным светом + импульс EMS + вибрационный массаж; выбран индивидуальный сервис</t>
+          <t>Характеристики: Л; Все включено послеоперационная обувь [одиночная]</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3186,18 +3114,18 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>190.00</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>190.00</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="R48" t="inlineStr"/>
@@ -3215,17 +3143,13 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Массажер для талии, фитнес-аппарат для интенсивной EMS-стимуляции, микротоковая согревающая компрессия, пояс для массажа талии с эффектом потоотделения во время тренировок.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01pEWgzJ1cun7PqAzzE_!!2219252433661-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Hong Kong Sheng Hooster Травма лодыжки фиксированная регулируемая подушка безопасности ахиллово сухожилие ботинки лодыжки</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F958578901827.html&amp;q=1&amp;t=1773241535783&amp;tep=FKFXRMKNN25573&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F778091504347.html&amp;q=1&amp;t=1773831956805&amp;tep=PFWXKQKNN25131114&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3234,28 +3158,28 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Характеристики: Спортивный пояс с импульсным подогревом и функцией обогрева; индивидуальный заказ.</t>
+          <t>Характеристики: XL; Черный</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="R49" t="inlineStr"/>
@@ -3273,17 +3197,13 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Массажер для ног Airwave, трансграничная поставка, английский язык, европейский стандарт, в наличии, односекционный автоматический массажер для икр с воздушной подушкой,</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01S8wvYS1cun6z7XLGQ_!!2219252433661-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Hong Kong Sheng Hooster Травма лодыжки фиксированная регулируемая подушка безопасности ахиллово сухожилие ботинки лодыжки</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773241535784&amp;tep=FKFXRMKNN1361417&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F778091504347.html&amp;q=1&amp;t=1773831956806&amp;tep=PFWXKQKNN2582012&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3292,28 +3212,28 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Характеристики: Европейский стандарт односекционной радиочастотной связи; выбран индивидуальный вариант обслуживания.</t>
+          <t>Характеристики: L; Черный</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>128.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>128.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>128.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="R50" t="inlineStr"/>
@@ -3331,17 +3251,13 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Массажер для ног Airwave, трансграничная поставка, английский язык, европейский стандарт, в наличии, односекционный автоматический массажер для икр с воздушной подушкой,</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN011NwqgX1cun6zEAPNN_!!2219252433661-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Hong Kong Sheng Hooster Травма лодыжки фиксированная регулируемая подушка безопасности ахиллово сухожилие ботинки лодыжки</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773241535785&amp;tep=FKFXRMKNN24202113&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F778091504347.html&amp;q=1&amp;t=1773831956807&amp;tep=PFWXKQKNN4151922&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -3350,28 +3266,28 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Характеристики: Европейский стандарт трехсекционного воздухозаборника; выбрана услуга индивидуальной настройки.</t>
+          <t>Характеристики: M; Черный</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>195.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>195.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>195.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="R51" t="inlineStr"/>
@@ -3389,17 +3305,13 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Массажер для ног Airwave, трансграничная поставка, английский язык, европейский стандарт, в наличии, односекционный автоматический массажер для икр с воздушной подушкой,</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN017Ter6J1cun6yu1Qgv_!!2219252433661-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Регулируемый плечевой и локтевой сустав фиксированная опорная линейка кронштейн для перелома царапин плечевой кости рука шина верхней конечности Защитное снаряжение для вывиха плеча</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773241535786&amp;tep=FKFXRMKNN2481926&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F704269019742.html&amp;q=1&amp;t=1773831956807&amp;tep=PFWXKQKNN313146&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -3408,28 +3320,28 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Характеристики: Европейский стандарт, английский двухступенчатая радиосвязь; выбран индивидуальный вариант обслуживания.</t>
+          <t>Характеристики: Свободный Размер; Крепежная Скоба для плечевого и локтевого суставов</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>350.00</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>350.00</t>
         </is>
       </c>
       <c r="R52" t="inlineStr"/>
@@ -3447,17 +3359,13 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Массажер для ног Airwave, трансграничная поставка, английский язык, европейский стандарт, в наличии, односекционный автоматический массажер для икр с воздушной подушкой,</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01VSqNER1cun6yb1kgC_!!2219252433661-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773241535787&amp;tep=FKFXRMKNN13132314&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773831956808&amp;tep=PFWXKQKNN1641013&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -3466,28 +3374,28 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Характеристики: Европейская фондовая биржа, английский язык, тепловая терапия колена, трехсекционная воздушная волна; индивидуальный подход к выбору услуг.</t>
+          <t>Характеристики: Слинг для взрослых; Справа.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>215.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>215.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>215.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="R53" t="inlineStr"/>
@@ -3505,17 +3413,13 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Статус:</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01nQ2daN1cun1qzbNHQ_!!2219252433661-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F884512282303.html&amp;q=1&amp;t=1773241535788&amp;tep=FKFXRMKNN2012238&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773831956809&amp;tep=PFWXKQKNN416726&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -3524,28 +3428,28 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Характеристики: Выбран индивидуальный сервис</t>
+          <t>Характеристики: Слинг для взрослых; Слева</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>192.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>192.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="R54" t="inlineStr"/>
@@ -3563,17 +3467,13 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Статус:</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01FGlPcQ1cun1r1Qpsv_!!2219252433661-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F884512282303.html&amp;q=1&amp;t=1773241535788&amp;tep=FKFXRMKNN2110146&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773831956809&amp;tep=PFWXKQKNN1518426&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -3582,28 +3482,28 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Характеристики: Выбран индивидуальный сервис</t>
+          <t>Характеристики: Взрослые; Справа.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>176.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>176.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R55" t="inlineStr"/>
@@ -3621,17 +3521,13 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01IP5xAN1gaPxPkIalE_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Крепление запястья для крепления запястья для защиты запястья для локтевой лучевой кости предплечья</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535789&amp;tep=FKFXRMKNN232610&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F790186347792.html&amp;q=1&amp;t=1773831956809&amp;tep=PFWXKQKNN1081114&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -3640,28 +3536,28 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле \Кошка\"] Набор из 5 штук магнитных форм пластырей для колена второго класса; 0000"</t>
+          <t>Характеристики: Взрослые; Слева</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R56" t="inlineStr"/>
@@ -3679,17 +3575,13 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01e1y6BI1gaPxP86g3C_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Регулируемая Скоба для фиксации локтевого сустава, опора для перелома руки, защита от вывиха руки, защита для послеоперационной реабилитации</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535790&amp;tep=FKFXRMKNN1624139&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F668295944038.html&amp;q=1&amp;t=1773831956810&amp;tep=PFWXKQKNN18181010&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -3698,28 +3590,28 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Характеристики: 0000 Цзан Цзы; 0000</t>
+          <t>Характеристики: Правильно; С поддержкой рук</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>170.00</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>170.00</t>
         </is>
       </c>
       <c r="R57" t="inlineStr"/>
@@ -3737,17 +3629,13 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01cg4ax11gaPxArRDkP_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Регулируемая Скоба для фиксации локтевого сустава, опора для перелома руки, защита от вывиха руки, защита для послеоперационной реабилитации</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535790&amp;tep=FKFXRMKNN5515&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F668295944038.html&amp;q=1&amp;t=1773831956810&amp;tep=PFWXKQKNN176256&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -3756,28 +3644,28 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Характеристики: 5 пластырей второго типа пластыря от мышечных и костных 0000</t>
+          <t>Характеристики: Слева; С поддержкой рук</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>170.00</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>170.00</t>
         </is>
       </c>
       <c r="R58" t="inlineStr"/>
@@ -3795,17 +3683,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Сжатые переломы грудной и поясничной стационарных позвонков</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01YHcf6e1gaPxBgMmlN_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01UZGT2m1XKXWzvQ9v4_!!2919502905-0-cib.jpg</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535791&amp;tep=FKFXRMKNN11232325&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F801057770124.html&amp;q=1&amp;t=1773831956811&amp;tep=PFWXKQKNN2620257&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -3814,28 +3702,28 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Характеристики: [Кошачий стиль — популярный стиль] Набор из 5 наплечных накладок Dr; 0000</t>
+          <t>Характеристики: XL; Дышащая двойная подушка безопасности</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="R59" t="inlineStr"/>
@@ -3853,17 +3741,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Сжатые переломы грудной и поясничной стационарных позвонков</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN015qYUea1gaPxDAcbm3_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01UZGT2m1XKXWzvQ9v4_!!2919502905-0-cib.jpg</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535792&amp;tep=FKFXRMKNN13191619&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F801057770124.html&amp;q=1&amp;t=1773831956811&amp;tep=PFWXKQKNN25261025&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -3872,28 +3760,28 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Характеристики: 0000</t>
+          <t>Характеристики: M; Дышащая двойная подушка безопасности</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="R60" t="inlineStr"/>
@@ -3911,17 +3799,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Сжатые переломы грудной и поясничной стационарных позвонков</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01XFJCPy1gaPxPjUnKs_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01UZGT2m1XKXWzvQ9v4_!!2919502905-0-cib.jpg</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535793&amp;tep=FKFXRMKNN21131516&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F801057770124.html&amp;q=1&amp;t=1773831956812&amp;tep=PFWXKQKNN96317&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -3930,28 +3818,28 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле кошки] 5 пластырей для контроля уровня сахара в крови и пластырей с магнитотерапией; 0000</t>
+          <t>Характеристики: L; Дышащая двойная подушка безопасности</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="R61" t="inlineStr"/>
@@ -3969,17 +3857,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Фиксированный бандаж бедра и колена Регулируемый тазобедренный сустав бедра травма коленного сустава предоперационная и послеоперационная фиксированная реабилитация</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01pnhhEL1gaPxPYy1kO_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/2020/188/163/19807361881_553590667.jpg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535794&amp;tep=FKFXRMKNN911114&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F625565395164.html&amp;q=1&amp;t=1773831956812&amp;tep=PFWXKQKNN2611010&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -3988,28 +3876,28 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Характеристики: 30 капстырей и 30 капсул бархатных пупочных пластырей из мокси Anzheng Jingpin; 0000</t>
+          <t>Характеристики: Свободный Размер; Левая и правая регулируемые</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>158.00</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>316.00</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>316.00</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
@@ -4027,17 +3915,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Электрическая массажная расческа вибрация красный свет инструмент для ухода за волосами</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01af8hmy1gaPxBsLYp0_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01LNVxw71aFuTARi4zJ_!!2214440683301-0-cib.jpg</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535795&amp;tep=FKFXRMKNN15243&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F925594684653.html&amp;q=1&amp;t=1773831956813&amp;tep=PFWXKQKNN222297&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -4046,28 +3934,28 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Характеристики: 0000 Ли Шичжень II категории; 0000</t>
+          <t>Характеристики: Английский; AA003 массажная расческа с распылителем (розовая)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>38.90</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>194.50</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>194.50</t>
         </is>
       </c>
       <c r="R63" t="inlineStr"/>
@@ -4085,17 +3973,13 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01uVMoKd1gaPxGbtO3y_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Мазь Баойинтанг Вэйфулин, оригинальный продукт, крем Вэйфулин, антибактериальная травяная мазь Вэйфулин для наружного применения, противозудная мазь</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535795&amp;tep=FKFXRMKNN248106&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F725110083300.html&amp;q=1&amp;t=1773831956813&amp;tep=PFWXKQKNN2161521&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -4104,7 +3988,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Характеристики: 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4114,18 +3998,18 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="R64" t="inlineStr"/>
@@ -4143,17 +4027,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Ядовитая кожа Король Антибактериальный крем Банг Бай Занят Яд Кожа Король Мазь Крем для кожи Натуральные товары</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN011klXGz1gaPx677Hn5_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01mvB0pe1Y0DUwz19g3_!!2209994362996-0-cib.jpg</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535796&amp;tep=FKFXRMKNN24262614&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F724775389538.html&amp;q=1&amp;t=1773831956813&amp;tep=PFWXKQKNN95823&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -4162,7 +4046,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Характеристики: 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4172,18 +4056,18 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="R65" t="inlineStr"/>
@@ -4201,17 +4085,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Kang Традиционная китайская медицина Хлоргексидин Ополаскиватель для полости рта Освежение полости рта Извлечение зубов Запах десен Пародонтальный зубной ополаскиватель Запах изо рта</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01oEMpeF1gaPxBSucdK_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01F8x3581Y0Deq1tiDr_!!2209994362996-0-cib.jpg</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535797&amp;tep=FKFXRMKNN18261814&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F902962451285.html&amp;q=1&amp;t=1773831956814&amp;tep=PFWXKQKNN7182610&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -4220,7 +4104,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле кошки] Набор из 5 расслабляющих пластырей для снижения напряжения с сухожилий второго класса; 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4230,18 +4114,18 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="R66" t="inlineStr"/>
@@ -4259,17 +4143,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Xianzhi Fu Ba Skin Poison Fresh Xianzhi Beijing Kangning Tianzhi Skin Poison Очищающая мазь против зуда кожи Крем Другие</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01OpS7t11gaPxQrODih_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01NrwnRM1Y0DirrJFWx_!!2209994362996-0-cib.jpg</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535798&amp;tep=FKFXRMKNN2221421&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1001577817475.html&amp;q=1&amp;t=1773831956814&amp;tep=PFWXKQKNN7231720&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -4278,7 +4162,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Характеристики: 100 г медицинской пасты для десен Факисерд; 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4288,18 +4172,18 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -4317,17 +4201,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Royal Grass Zhen Ding B Оральная паста 65 г/тюбик для пародонтального ухода за красными и опухшими деснами, зубная паста Kangchining, антибактериальный тип Kang Traditional Chinese Medicine.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01JGL2gB1gaPxPwtevS_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01Q72Z7W1Y0DeoiB3oN_!!2209994362996-0-cib.jpg</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535798&amp;tep=FKFXRMKNN310814&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F902965743360.html&amp;q=1&amp;t=1773831956815&amp;tep=PFWXKQKNN2020816&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -4336,7 +4220,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в кошачьем стиле] 50 мл Anzheng Jingpin Snake Bone Wudu Muscle Spirit; 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4346,18 +4230,18 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="R68" t="inlineStr"/>
@@ -4375,17 +4259,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Shulijia ядовитый крем Цзянси Хон Хай травяная мазь для внешнего ухода за кожей мазь в наличии оптом</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN013JEHDM1gaPxBHIy1S_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01eOpV341Vv3gj6Nd3o_!!2210100902714-0-cib.jpg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535799&amp;tep=FKFXRMKNN22221024&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F725115135011.html&amp;q=1&amp;t=1773831956815&amp;tep=PFWXKQKNN19239&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -4394,7 +4278,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле кошки] 5-пакетный совместный патч Qiongfang второго класса для приюта; 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4404,18 +4288,18 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>17.20</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>17.20</t>
         </is>
       </c>
       <c r="R69" t="inlineStr"/>
@@ -4433,17 +4317,13 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN018c9sK11gaPxOqrccB_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Назальный спрей с травяным прополисом Snow Mountain для освежающего и успокаивающего облегчения за полминуты.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535800&amp;tep=FKFXRMKNN259252&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F993297925846.html&amp;q=1&amp;t=1773831956816&amp;tep=PFWXKQKNN22293&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -4452,7 +4332,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле кошек] 8 пластырей для облегчения срабатывания с дальним инфракрасным 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4462,18 +4342,18 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="R70" t="inlineStr"/>
@@ -4491,17 +4371,13 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01oEaqAV1gaPxPjx6mF_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Guangzhide крем с ядом скорпиона яд скорпиона травяная внешняя противозудящая кремовая мазь</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535801&amp;tep=FKFXRMKNN1616183&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F724930778595.html&amp;q=1&amp;t=1773831956816&amp;tep=PFWXKQKNN651626&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -4510,7 +4386,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Характеристики: [Горячая модель в стиле кошки] 8 пластырей второго типа Ли Шичжэнь Panax notoginseng и пластырей с ядом 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4520,18 +4396,18 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="R71" t="inlineStr"/>
@@ -4549,17 +4425,13 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01apE9Ff1gaPxKY0ggA_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Крем Bangbai Mangbaodu Baowang Baodu Baowang Крем для кожи Травяной наружный крем против зуда и зуда</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535802&amp;tep=FKFXRMKNN14172111&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F651595883228.html&amp;q=1&amp;t=1773831956816&amp;tep=PFWXKQKNN1526716&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -4568,28 +4440,28 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Характеристики: 10 наклеек тайской сороконожки; 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>43.60</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>43.60</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
@@ -4607,17 +4479,13 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01LyUPEn1gaPxQ6pP2N_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Крем-мазь Miao Jia Langzhong для наружного применения, травяной крем для кожи Miao Jia Langzhong</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535803&amp;tep=FKFXRMKNN14191525&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F645399027304.html&amp;q=1&amp;t=1773831956817&amp;tep=PFWXKQKNN86714&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -4626,7 +4494,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Характеристики: 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4636,18 +4504,18 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>21.80</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>21.80</t>
         </is>
       </c>
       <c r="R73" t="inlineStr"/>
@@ -4665,17 +4533,13 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01cl2vac1gaPxBrUwcE_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Ледяная волна ледяной Шелкопряд Детский травяной крем ледяной Шелкопряд детская кожа Внешний антизудящий мазь крем</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535803&amp;tep=FKFXRMKNN1232424&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F642315882168.html&amp;q=1&amp;t=1773831956817&amp;tep=PFWXKQKNN102221&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -4684,7 +4548,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле кошки] 5 упаковок поясничных пластырей Qiongfang для приюта второго класса; 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4694,18 +4558,18 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="R74" t="inlineStr"/>
@@ -4723,17 +4587,13 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01gC0Jig1gaPxP8O8IU_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Зарубежный крем Чичеллы тысячелетия, внешний крем для кожи, внешний крем для кожи чичеллы тысячелетия, крем против зуда, цельный</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535804&amp;tep=FKFXRMKNN24242218&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F659242299733.html&amp;q=1&amp;t=1773831956818&amp;tep=PFWXKQKNN157219&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -4742,7 +4602,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Характеристики: 0000</t>
+          <t>Характеристики: 无规格</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -4752,18 +4612,18 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="R75" t="inlineStr"/>
@@ -4781,17 +4641,13 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01khgdPQ1gaPxVXf3CS_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Чистый хлопок полыни наколенники для мужчин и женщин теплые Бесшовные тонкие коленные суставы оболочки старые холодные ноги лихорадка наколенники</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535804&amp;tep=FKFXRMKNN8232118&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F731863776117.html&amp;q=1&amp;t=1773831956819&amp;tep=PFWXKQKNN232219&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -4800,28 +4656,28 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле \Кошка\"] 15 г медицинский увлажняющий пластырь для губ с 0000"</t>
+          <t>Характеристики: Свободный размер [4000 кг-7500 кг]; Серый + Серый [2 пары]</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="R76" t="inlineStr"/>
@@ -4839,17 +4695,13 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01WFBKI91gaPxBwMJbc_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Чистый хлопок полыни наколенники для мужчин и женщин теплые Бесшовные тонкие коленные суставы оболочки старые холодные ноги лихорадка наколенники</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535805&amp;tep=FKFXRMKNN21122216&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F731863776117.html&amp;q=1&amp;t=1773831956819&amp;tep=PFWXKQKNN1082316&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -4858,28 +4710,28 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле Cat] 5 штук, пластырь для шейного отдела второго класса второго класса, 0000</t>
+          <t>Характеристики: Свободный размер [4000 кг-7500 кг]; Цвет кожи + цвет кожи [2]</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="R77" t="inlineStr"/>
@@ -4897,17 +4749,13 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01O3NC7l1gaPxPjd7Iv_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Наколенник на шнуровке с подогревом полыни старые холодные ноги теплый ФИЗИОТЕРАПЕВТИЧЕСКИЙ спортивный чехол для ног давление Спортивный нескользящий наколенник для мужчин и женщин</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535806&amp;tep=FKFXRMKNN21712&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F684403797511.html&amp;q=1&amp;t=1773831956820&amp;tep=PFWXKQKNN208265&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -4916,28 +4764,28 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле кота] Гель для коленей Li Shizhen, 20 г; 0000</t>
+          <t>Характеристики: Размер М ( 40-60kg ); Пара полынь с длинными ремешками (оранжевый)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>32.50</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>32.50</t>
         </is>
       </c>
       <c r="R78" t="inlineStr"/>
@@ -4955,17 +4803,13 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
-        </is>
-      </c>
+          <t>Массажер для талии с воздушными подушками, подтягивающий и растягивающий, с вибрационной поддержкой поясницы, вибрацией для спины, для домашнего использования, с горячим компрессом, импульсный массажер для поясничного отдела позвоночника</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535806&amp;tep=FKFXRMKNN23202510&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F921340341364.html&amp;q=1&amp;t=1773831956821&amp;tep=PFWXKQKNN2511720&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -4974,28 +4818,28 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярная модель в стиле кошки] 20 г, тип 2, Ли Шичжэнь, дальний инфракрасный суставной 0000</t>
+          <t>Характеристики: Эксклюзивная модель Green - массаж верхней части талии + горячий компресс с красным светом + импульс EMS + вибрационный массаж;已选定制服务</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>190.00</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>190.00</t>
         </is>
       </c>
       <c r="R79" t="inlineStr"/>
@@ -5013,17 +4857,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>Массажер для талии, фитнес-устройство EMS, импульсный массажер для всего тела, микротоковый массажер с подогревом и компрессией, пояс для упражнений и массажа с функцией стимуляции потоотделения</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01VYlxpm1gaPxBemTot_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01pEWgzJ1cun7PqAzzE_!!2219252433661-0-cib.jpg</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535807&amp;tep=FKFXRMKNN123179&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F958578901827.html&amp;q=1&amp;t=1773831956821&amp;tep=PFWXKQKNN20121620&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -5032,28 +4876,28 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Характеристики: [Горячая модель в стиле кошки] 20 г, тип 2, гель для отключения дальнего инфракрасного излучения Li Shizhen, зеленая коробка; 0000</t>
+          <t>Характеристики: Спортивный пояс с горячим компрессом и пульсацией;已选定制服务</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>350.00</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>350.00</t>
         </is>
       </c>
       <c r="R80" t="inlineStr"/>
@@ -5071,17 +4915,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>空气波腿部按摩器跨境英文欧规现货单节小腿气囊包裹全自动按摩仪</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN017Ogr4o1gaPxPClghF_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01S8wvYS1cun6z7XLGQ_!!2219252433661-0-cib.jpg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535808&amp;tep=FKFXRMKNN229236&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773831956822&amp;tep=PFWXKQKNN511111&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -5090,28 +4934,28 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Характеристики: [Популярный продукт в стиле «Кошка»] Увлажняющий крем для здоровья с растительными экстрактами, 50 мл, Schnai Pharmaceutical; 0000</t>
+          <t>Характеристики: 欧规英文单节空气波;已选定制服务</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>128.00</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>128.00</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>128.00</t>
         </is>
       </c>
       <c r="R81" t="inlineStr"/>
@@ -5129,17 +4973,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[Хит продаж] Пластырь для шейного отдела костюма, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейный отдел костюма, Специальный пластырь</t>
+          <t>空气波腿部按摩器跨境英文欧规现货单节小腿气囊包裹全自动按摩仪</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN019u14nT1gaPxCROTNw_!!2220071954158-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN011NwqgX1cun6zEAPNN_!!2219252433661-0-cib.jpg</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773241535810&amp;tep=FKFXRMKNN2391613&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773831956823&amp;tep=PFWXKQKNN1917822&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -5148,28 +4992,28 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Характеристики: [Кошачий стиль, популярная модель] Набор из 6 модифицированных пластырей для предотвращения 0000</t>
+          <t>Характеристики: 欧规英文三节空气波;已选定制服务</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
@@ -5187,17 +5031,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Пластыри с глюкозамином и хондроитином от производителя: эластичные тканевые пластыри для шеи, поясничного отдела позвоночника и коленей, пластыри с глюкозамином, хондроитином и кальцием.</t>
+          <t>空气波腿部按摩器跨境英文欧规现货单节小腿气囊包裹全自动按摩仪</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01JEOzy3228PByqhL2L_!!2215056697075-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN017Ter6J1cun6yu1Qgv_!!2219252433661-0-cib.jpg</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F874066608460.html&amp;q=1&amp;t=1773241535811&amp;tep=FKFXRMKNN1216174&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773831956823&amp;tep=PFWXKQKNN2018221&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -5206,28 +5050,28 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Характеристики: Пластырь с глюкозамином и хондроитином</t>
+          <t>Характеристики: 欧规英文双节空气波;已选定制服务</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="R83" t="inlineStr"/>
@@ -5245,17 +5089,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Кодонопсис пилозула, смешанная</t>
+          <t>空气波腿部按摩器跨境英文欧规现货单节小腿气囊包裹全自动按摩仪</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01iZcxAv228PFqF4nlI_!!2215056697075-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01VSqNER1cun6yb1kgC_!!2219252433661-0-cib.jpg</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F709555726673.html&amp;q=1&amp;t=1773241535811&amp;tep=FKFXRMKNN761222&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1007168595338.html&amp;q=1&amp;t=1773831956824&amp;tep=PFWXKQKNN461816&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -5264,28 +5108,28 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Характеристики: 8 монтаж; Партия женьшень метеоризм</t>
+          <t>Характеристики: 欧股英文膝盖热敷三节空气波;已选定制服务</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
@@ -5303,17 +5147,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Японский фармацевтический пластырь Toki Pharmaceutical с дальним инфракрасным излучением для лечения острого и хронического бронхита, бронхиальной астмы и кашля.</t>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01tfrlvL1v5130IZEvj_!!2220717196120-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01IP5xAN1gaPxPkIalE_!!2220071954158-0-cib.jpg</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1027004760058.html&amp;q=1&amp;t=1773241535812&amp;tep=FKFXRMKNN206213&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956824&amp;tep=PFWXKQKNN1412202&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -5322,7 +5166,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Характеристики: Одна упаковка бронхиальных пластырей Dongqi Pharmaceutical.</t>
+          <t>Характеристики: [Популярная модель в стиле "Cat"] Набор из 5 штук магнитных терапевтических пластырей для колен второго класса; 0000</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5332,18 +5176,18 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="R85" t="inlineStr"/>
@@ -5361,17 +5205,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Пластыри Miaojia с цветочным узором для поясницы от производителя, большие пластыри для поясниц на грыже межпозвоночного диска и болях сзади.</t>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN010fz0WT1Z8IF4bJ65o_!!2208529943149-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01e1y6BI1gaPxP86g3C_!!2220071954158-0-cib.jpg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F951328948318.html&amp;q=1&amp;t=1773241535812&amp;tep=FKFXRMKNN2072211&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956825&amp;tep=PFWXKQKNN23111023&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -5380,7 +5224,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Характеристики: 17х25 см</t>
+          <t>Характеристики: [Популярная модель в стиле кота] 6 пластырей для ушей Zang Zi; 0000</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5390,18 +5234,18 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -5419,17 +5263,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Обезболивающий пластырь производства Miao Medicine, универсальный миорелаксант и стимулятор кровообращения, для массажа коленного сустава, согревающий и проникающий в кости пластырь,</t>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://cbu01.alicdn.com/img/ibank/O1CN01JfmmJV1Z8IFBCRUoj_!!2208529943149-0-cib.jpg</t>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01cg4ax11gaPxArRDkP_!!2220071954158-0-cib.jpg</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F851358339501.html&amp;q=1&amp;t=1773241535813&amp;tep=FKFXRMKNN31449&amp;cn=e-c&amp;from=shopping_cart_export</t>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956825&amp;tep=PFWXKQKNN1512249&amp;cn=e-c&amp;from=shopping_cart_export</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -5438,33 +5282,1695 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Характеристики: Пластырь от боли Du Miao; 30 г</t>
+          <t>Характеристики: [Популярная модель в стиле кошки] 5 пластырей второго типа пластыря от мышечных и костных болей Ли Шичжэня; 0000</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01YHcf6e1gaPxBgMmlN_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956825&amp;tep=PFWXKQKNN124196&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Характеристики: [Cat style — популярный стиль] Набор из 5 наплечных накладок Dr; 0000</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>10</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN015qYUea1gaPxDAcbm3_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956826&amp;tep=PFWXKQKNN251269&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кота] Синяя коробка второго типа на плечо, 5 шт.; 0000</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>10</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01XFJCPy1gaPxPjUnKs_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956826&amp;tep=PFWXKQKNN10132021&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] 5 пластырей для контроля уровня сахара в крови и пластырей с магнитотерапией; 0000</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>10</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956827&amp;tep=PFWXKQKNN1024819&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в кошачьем стиле] 30 пластырей и 30 капсул бархатных пупочных пластырей из моксы Anzheng Jingpin; 0000</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>10</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956827&amp;tep=PFWXKQKNN26161126&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] 6 упаковок пластырей для мышц и костей Li Shizhen II категории; 0000</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="n">
+        <v>10</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956828&amp;tep=PFWXKQKNN2412217&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] 5 штук пластыря для простаты Ли Шичжэнь; 0000</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>10</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956828&amp;tep=PFWXKQKNN62169&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] Комплект из 3-х штук для заживления анальных ран; 0000</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>10</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>38.00</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>38.00</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956829&amp;tep=PFWXKQKNN112326&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] Набор из 5 расслабляющих пластырей для снятия напряжения с сухожилий второго класса; 0000</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="n">
+        <v>10</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956829&amp;tep=PFWXKQKNN18261714&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле Cat] 100 г медицинской пасты для десен Fakiserd; 0000</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="n">
+        <v>10</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01JGL2gB1gaPxPwtevS_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956829&amp;tep=PFWXKQKNN351410&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в кошачьем стиле] 50 мл Anzheng Jingpin Snake Bone Wudu Muscle Spirit; 0000</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="n">
+        <v>10</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN013JEHDM1gaPxBHIy1S_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956830&amp;tep=PFWXKQKNN63418&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] 5-пакетный совместный патч Qiongfang второго класса для приюта; 0000</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="n">
+        <v>10</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN018c9sK11gaPxOqrccB_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956830&amp;tep=PFWXKQKNN1731812&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] 8 пластырей для облегчения астмы с дальним инфракрасным излучением Ли Шичжэня; 0000</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="n">
+        <v>10</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01oEaqAV1gaPxPjx6mF_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956831&amp;tep=PFWXKQKNN1792113&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Характеристики: [Горячая модель в стиле кошки] 8 пластырей второго типа Ли Шичжэнь Panax notoginseng и пластырей с ядом скорпиона, проникающих в кости; 0000</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="n">
+        <v>10</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01apE9Ff1gaPxKY0ggA_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956831&amp;tep=PFWXKQKNN1392415&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярный стиль кошки] 10 наклеек тайской сороконожки; 0000</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="n">
+        <v>10</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>38.00</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>38.00</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01LyUPEn1gaPxQ6pP2N_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956832&amp;tep=PFWXKQKNN2117215&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярный продукт в стиле Cat] 20 г Sna Pharmaceutical Aluminum Chlorohydrex Антиперспирант-дезодорирующий крем; 0000</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="n">
+        <v>10</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01cl2vac1gaPxBrUwcE_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956832&amp;tep=PFWXKQKNN1621198&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] 5 упаковок поясничных пластырей Qiongfang для приюта второго класса; 0000</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="n">
+        <v>10</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01gC0Jig1gaPxP8O8IU_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956832&amp;tep=PFWXKQKNN246262&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярный продукт в стиле кошки] 30 мл спрей для расслабления ног с хитозаном Anzhengjingpin; 0000</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>10</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01khgdPQ1gaPxVXf3CS_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956833&amp;tep=PFWXKQKNN211266&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле "Cat"] 15 г медицинский увлажняющий пластырь для губ с полиэтиленгликолем; 0000</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="n">
+        <v>10</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01WFBKI91gaPxBwMJbc_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956834&amp;tep=PFWXKQKNN258120&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле Cat] 5 штук, пластырь для шейного отдела позвоночника второго класса, универсальный пластырь для всего тела; 0000</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>10</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01O3NC7l1gaPxPjd7Iv_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956834&amp;tep=PFWXKQKNN6462&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кота] Гель для коленей Li Shizhen, 20 г; 0000</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>10</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN016opedG1gaPxE2nVtU_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956835&amp;tep=PFWXKQKNN4161321&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярная модель в стиле кошки] 20 г, тип 2, Ли Шичжэнь, дальний инфракрасный суставной гель, цвет травы; 0000</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>10</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956836&amp;tep=PFWXKQKNN161972&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Характеристики: [Горячая модель в стиле кошки] 20 г, тип 2, гель для отключения дальнего инфракрасного излучения Li Shizhen, зеленая коробка; 0000</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>10</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956836&amp;tep=PFWXKQKNN8771&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Характеристики: [Популярный продукт в стиле "Cat"] Увлажняющий крем для здоровья с растительными экстрактами, 50 мл, Schnai Pharmaceutical; 0000</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>10</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>[Хит продаж] Пластырь для шейного отдела позвоночника, пластырь для лечения дальнего инфракрасного излучения, 5 пластырей, противовоспалительный и обезболивающий пластырь для плеча, шейного отдела позвоночника, специальный пластырь</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://cbu01.alicdn.com/img/ibank/O1CN01yakpvs1gaPxFWfEjW_!!2220071954158-0-cib.jpg</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F984990167713.html&amp;q=1&amp;t=1773831956837&amp;tep=PFWXKQKNN4111212&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Характеристики: [Cat style, популярная модель] Набор из 6 усовершенствованных пластырей для предотвращения протекания мочи; 0000</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="n">
+        <v>10</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Аммиак хондроитин производитель производитель шейных суставов поясничного отдела позвоночника колена эластичная пластырь аммиака хондроитин кальций</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F874066608460.html&amp;q=1&amp;t=1773831956838&amp;tep=PFWXKQKNN1726148&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Характеристики: Пластырь хондроитина аммиака1</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>10</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Кодонопсис пилозула, смешанная</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F709555726673.html&amp;q=1&amp;t=1773831956838&amp;tep=PFWXKQKNN2016726&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Характеристики: 8 монтаж; Партия женьшень метеоризм</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>10</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Японский фармацевтический пластырь Toki Pharmaceutical с дальним инфракрасным излучением для лечения острого и хронического бронхита, бронхиальной астмы и кашля.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F1027004760058.html&amp;q=1&amp;t=1773831956839&amp;tep=PFWXKQKNN132265&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Характеристики: Одна упаковка бронхиальных пластырей Dongqi Pharmaceutical.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>10</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Пластыри Miaojia с цветочным узором для поясницы от производителя, большие пластыри для поясниц на грыже межпозвоночного диска и болях сзади.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F951328948318.html&amp;q=1&amp;t=1773831956839&amp;tep=PFWXKQKNN251811&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Характеристики: 17х25 см</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>10</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>31.50</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>31.50</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>+380936174140</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Мазь Мяо Яо Цупэн, от производителя, универсальная мазью для расслабления мышц рук и улучшения кровообращения, подходит для массажа коленей и суставов, обладает смешанной</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.aliprice.com/Index/detail.html?url=https%3A%2F%2Fdetail.1688.com%2Foffer%2F851358339501.html&amp;q=1&amp;t=1773831956840&amp;tep=PFWXKQKNN18191720&amp;cn=e-c&amp;from=shopping_cart_export</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Характеристики: 30 г;</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>5</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>6.80</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
